--- a/statements.xlsx
+++ b/statements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d13a3759e55e9fe4/Documentos/PROJECT_FOLDER/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{1811E269-FA36-46C7-9CD7-57300936F644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19F116FF-AA0C-42C6-9B8E-5B9B6818A3E2}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{1811E269-FA36-46C7-9CD7-57300936F644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72E94CCA-CC36-4C86-B27F-F9CCA89697AA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ADF165DB-61D8-4109-9F78-D3C5531ECE30}"/>
   </bookViews>
@@ -76,12 +76,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="391">
   <si>
     <t>Receipt No</t>
-  </si>
-  <si>
-    <t>Completion Time</t>
   </si>
   <si>
     <t>Details</t>
@@ -1241,16 +1238,37 @@
   </si>
   <si>
     <t>Customer Payment to Small Business to 0792***832 - JOSHUA PETER OPONDO</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Date3</t>
+  </si>
+  <si>
+    <t>Time2</t>
+  </si>
+  <si>
+    <t>Completion Date Time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1276,9 +1294,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1312,31 +1331,40 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_10" connectionId="1" xr16:uid="{34D5CC93-AC77-4317-816C-40C56F128740}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="8">
-    <queryTableFields count="7">
+  <queryTableRefresh nextId="16" unboundColumnsRight="3">
+    <queryTableFields count="10">
       <queryTableField id="1" name="Receipt No" tableColumnId="1"/>
-      <queryTableField id="2" name="Completion Time" tableColumnId="2"/>
+      <queryTableField id="15" dataBound="0" tableColumnId="13"/>
       <queryTableField id="3" name="Details" tableColumnId="3"/>
       <queryTableField id="4" name="Transaction Status" tableColumnId="4"/>
       <queryTableField id="5" name="Paid in" tableColumnId="5"/>
       <queryTableField id="6" name="Withdraw n" tableColumnId="6"/>
       <queryTableField id="7" name="Balance" tableColumnId="7"/>
+      <queryTableField id="8" dataBound="0" tableColumnId="8"/>
+      <queryTableField id="9" dataBound="0" tableColumnId="9"/>
+      <queryTableField id="10" dataBound="0" tableColumnId="10"/>
     </queryTableFields>
+    <queryTableDeletedFields count="1">
+      <deletedField name="Completion Time"/>
+    </queryTableDeletedFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E9B7E87B-4DA9-4CF4-BA8E-0CF130EE6611}" name="Append1" displayName="Append1" ref="A1:G260" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:G260" xr:uid="{E9B7E87B-4DA9-4CF4-BA8E-0CF130EE6611}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E9B7E87B-4DA9-4CF4-BA8E-0CF130EE6611}" name="Append1" displayName="Append1" ref="A1:J260" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:J260" xr:uid="{E9B7E87B-4DA9-4CF4-BA8E-0CF130EE6611}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{D8971954-E9D7-4B10-988F-3D0521417991}" uniqueName="1" name="Receipt No" queryTableFieldId="1" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{CCCE556B-1031-4B9F-838B-B48744B6E727}" uniqueName="2" name="Completion Time" queryTableFieldId="2" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{F2D0991C-37A9-42D8-A97A-5679B81FA22D}" uniqueName="13" name="Completion Date Time" queryTableFieldId="15" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{CEA7FEA0-6B4C-4D02-B94D-83E621A1E963}" uniqueName="3" name="Details" queryTableFieldId="3" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{2B431927-8648-4FED-9ABB-7CC2777E5496}" uniqueName="4" name="Transaction Status" queryTableFieldId="4" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{49BF6AD2-A17A-48F3-8387-E931033784BE}" uniqueName="5" name="Paid in" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{A96E8048-4DC7-41DF-9521-0AC082689DD3}" uniqueName="6" name="Withdraw n" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{6563FC33-F498-4FB5-946D-487893BD0815}" uniqueName="7" name="Balance" queryTableFieldId="7"/>
+    <tableColumn id="8" xr3:uid="{010252D5-45BF-48D6-8E0F-0D89D89DCF02}" uniqueName="8" name="Date" queryTableFieldId="8"/>
+    <tableColumn id="9" xr3:uid="{C4C80A81-7031-44EB-BBF8-FA5C40F9F297}" uniqueName="9" name="Time2" queryTableFieldId="9"/>
+    <tableColumn id="10" xr3:uid="{083ED6F4-0C96-41D1-A9F0-65C47F62443F}" uniqueName="10" name="Date3" queryTableFieldId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1639,52 +1667,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE94CB6B-0BDC-454D-ABB0-1E8AC7920C44}">
-  <dimension ref="A1:G260"/>
+  <dimension ref="A1:J260"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="80.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>387</v>
+      </c>
+      <c r="I1" t="s">
+        <v>389</v>
+      </c>
+      <c r="J1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="2">
-        <v>45990.903472002312</v>
+        <v>112</v>
+      </c>
+      <c r="B2" s="3">
+        <v>45990.90347222222</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -1696,18 +1733,18 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="3">
+        <v>45990.871527777781</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="2">
-        <v>45990.871527997682</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1719,18 +1756,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" s="2">
-        <v>45990.867360995369</v>
+        <v>115</v>
+      </c>
+      <c r="B4" s="3">
+        <v>45990.867361111108</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1742,18 +1779,18 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="3">
+        <v>45990.86041666667</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B5" s="2">
-        <v>45990.860417002317</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1765,18 +1802,18 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" s="2">
-        <v>45990.859722002315</v>
+        <v>118</v>
+      </c>
+      <c r="B6" s="3">
+        <v>45990.859722222223</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -1788,18 +1825,18 @@
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="2">
-        <v>45990.855555995367</v>
+        <v>119</v>
+      </c>
+      <c r="B7" s="3">
+        <v>45990.855555555558</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1811,18 +1848,18 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="3">
+        <v>45990.854861111111</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="2">
-        <v>45990.854860995372</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1834,18 +1871,18 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="3">
+        <v>45990.818749999999</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="2">
-        <v>45990.818749999999</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1857,18 +1894,18 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="2">
-        <v>45990.818055995369</v>
+        <v>124</v>
+      </c>
+      <c r="B10" s="3">
+        <v>45990.818055555559</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>200</v>
@@ -1880,18 +1917,18 @@
         <v>223</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="3">
+        <v>45990.8125</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B11" s="2">
-        <v>45990.8125</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1903,18 +1940,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="3">
+        <v>45990.765972222223</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B12" s="2">
-        <v>45990.765972002315</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1926,18 +1963,18 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="3">
+        <v>45990.748611111114</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="2">
-        <v>45990.748610995368</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1949,18 +1986,18 @@
         <v>183</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B14" s="2">
-        <v>45990.706944004633</v>
+        <v>131</v>
+      </c>
+      <c r="B14" s="3">
+        <v>45990.706944444442</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1972,18 +2009,18 @@
         <v>203</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="3">
+        <v>45990.355555555558</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B15" s="2">
-        <v>45990.355555995367</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1995,18 +2032,18 @@
         <v>213</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="3">
+        <v>45990.310416666667</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B16" s="2">
-        <v>45990.310417002314</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2020,16 +2057,16 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="3">
+        <v>45990.293055555558</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="2">
-        <v>45990.293055995367</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="D17" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2043,16 +2080,16 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="2">
-        <v>45990.290972002316</v>
+        <v>138</v>
+      </c>
+      <c r="B18" s="3">
+        <v>45990.290972222225</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18">
         <v>350</v>
@@ -2066,16 +2103,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B19" s="2">
-        <v>45989.884722002316</v>
+        <v>139</v>
+      </c>
+      <c r="B19" s="3">
+        <v>45989.884722222225</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2089,16 +2126,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B20" s="2">
-        <v>45989.882639004631</v>
+        <v>140</v>
+      </c>
+      <c r="B20" s="3">
+        <v>45989.882638888892</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2112,16 +2149,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B21" s="2">
-        <v>45989.876389004632</v>
+        <v>141</v>
+      </c>
+      <c r="B21" s="3">
+        <v>45989.876388888886</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2135,16 +2172,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" s="3">
+        <v>45989.809027777781</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="2">
-        <v>45989.809027997682</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2158,16 +2195,16 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" s="2">
-        <v>45989.809027997682</v>
+        <v>144</v>
+      </c>
+      <c r="B23" s="3">
+        <v>45989.809027777781</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2181,16 +2218,16 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="3">
+        <v>45989.791666666664</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B24" s="2">
-        <v>45989.791667002311</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2204,16 +2241,16 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B25" s="2">
-        <v>45989.790277997687</v>
+        <v>147</v>
+      </c>
+      <c r="B25" s="3">
+        <v>45989.790277777778</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>200</v>
@@ -2227,16 +2264,16 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="3">
+        <v>45989.770138888889</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="2">
-        <v>45989.770139004628</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2250,16 +2287,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" s="3">
+        <v>45989.347222222219</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B27" s="2">
-        <v>45989.347222002318</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2273,16 +2310,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" s="2">
+        <v>152</v>
+      </c>
+      <c r="B28" s="3">
         <v>45989.34375</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2296,16 +2333,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" s="3">
+        <v>45989.28402777778</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B29" s="2">
-        <v>45989.284027997688</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="D29" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2319,16 +2356,16 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" s="3">
+        <v>45989.277083333334</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="2">
-        <v>45989.277082997687</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2342,16 +2379,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" s="3">
+        <v>45989.229861111111</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B31" s="2">
-        <v>45989.229860995372</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="D31" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2365,16 +2402,16 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B32" s="2">
-        <v>45989.228472002316</v>
+        <v>159</v>
+      </c>
+      <c r="B32" s="3">
+        <v>45989.228472222225</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E32">
         <v>300</v>
@@ -2388,16 +2425,16 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B33" s="2">
-        <v>45988.902777997682</v>
+        <v>160</v>
+      </c>
+      <c r="B33" s="3">
+        <v>45988.902777777781</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2411,16 +2448,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B34" s="2">
+        <v>161</v>
+      </c>
+      <c r="B34" s="3">
         <v>45988.9</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2434,16 +2471,16 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="3">
+        <v>45988.88958333333</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="2">
-        <v>45988.889582997683</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2457,16 +2494,16 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" s="2">
-        <v>45988.889582997683</v>
+        <v>9</v>
+      </c>
+      <c r="B36" s="3">
+        <v>45988.88958333333</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2480,16 +2517,16 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="3">
+        <v>45988.888888888891</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B37" s="2">
-        <v>45988.888889004629</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="D37" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E37">
         <v>100</v>
@@ -2503,16 +2540,16 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="3">
+        <v>45988.836111111108</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="2">
-        <v>45988.836110995369</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="D38" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2526,16 +2563,16 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="3">
+        <v>45988.762499999997</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B39" s="2">
-        <v>45988.762499999997</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="D39" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2549,16 +2586,16 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="2">
-        <v>45988.759027997687</v>
+        <v>16</v>
+      </c>
+      <c r="B40" s="3">
+        <v>45988.759027777778</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E40">
         <v>100</v>
@@ -2572,16 +2609,16 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="3">
+        <v>45988.744444444441</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="2">
-        <v>45988.744444004631</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D41" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2595,16 +2632,16 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B42" s="2">
-        <v>45988.715277997682</v>
+        <v>19</v>
+      </c>
+      <c r="B42" s="3">
+        <v>45988.715277777781</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2618,16 +2655,16 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="3">
+        <v>45988.638888888891</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B43" s="2">
-        <v>45988.638889004629</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="D43" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2641,16 +2678,16 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B44" s="2">
-        <v>45988.636805995367</v>
+        <v>22</v>
+      </c>
+      <c r="B44" s="3">
+        <v>45988.636805555558</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2664,16 +2701,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="3">
+        <v>45988.635416666664</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="2">
-        <v>45988.635417002311</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D45" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2687,16 +2724,16 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" s="3">
+        <v>45988.588888888888</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B46" s="2">
-        <v>45988.588889004626</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D46" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E46">
         <v>100</v>
@@ -2710,16 +2747,16 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="3">
+        <v>45988.410416666666</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B47" s="2">
-        <v>45988.410417002313</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D47" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2733,16 +2770,16 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" s="3">
+        <v>45987.865972222222</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B48" s="2">
-        <v>45987.865972002313</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D48" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2756,16 +2793,16 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" s="3">
+        <v>45987.862500000003</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B49" s="2">
-        <v>45987.862500000003</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="D49" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2779,16 +2816,16 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" s="3">
+        <v>45987.854861111111</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B50" s="2">
-        <v>45987.854860995372</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="D50" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2802,16 +2839,16 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="3">
+        <v>45987.789583333331</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B51" s="2">
-        <v>45987.789582997684</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="D51" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2825,16 +2862,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="2">
-        <v>45987.789582997684</v>
+        <v>37</v>
+      </c>
+      <c r="B52" s="3">
+        <v>45987.789583333331</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E52">
         <v>200</v>
@@ -2848,16 +2885,16 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="2">
-        <v>45987.788889004631</v>
+        <v>38</v>
+      </c>
+      <c r="B53" s="3">
+        <v>45987.788888888892</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2871,16 +2908,16 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3">
+        <v>45987.76666666667</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B54" s="2">
-        <v>45987.766667002317</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="D54" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2894,16 +2931,16 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3">
+        <v>45987.678472222222</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B55" s="2">
-        <v>45987.678472002313</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="D55" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2917,16 +2954,16 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" s="3">
+        <v>45987.363888888889</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B56" s="2">
-        <v>45987.363889004628</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="D56" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2940,16 +2977,16 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="3">
+        <v>45987.31527777778</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="2">
-        <v>45987.315277997688</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="D57" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2963,16 +3000,16 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B58" s="3">
+        <v>45987.288888888892</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B58" s="2">
-        <v>45987.288889004631</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="D58" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2986,16 +3023,16 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B59" s="3">
+        <v>45986.909722222219</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B59" s="2">
-        <v>45986.909722002318</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D59" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3009,16 +3046,16 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B60" s="3">
+        <v>45986.90625</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B60" s="2">
-        <v>45986.90625</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="D60" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3032,16 +3069,16 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B61" s="2">
-        <v>45986.902082997687</v>
+        <v>53</v>
+      </c>
+      <c r="B61" s="3">
+        <v>45986.902083333334</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3055,16 +3092,16 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B62" s="3">
+        <v>45986.627083333333</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B62" s="2">
-        <v>45986.627082997686</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="D62" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3078,16 +3115,16 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63" s="3">
+        <v>45986.625694444447</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B63" s="2">
-        <v>45986.62569400463</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="D63" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3101,16 +3138,16 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B64" s="3">
+        <v>45986.622916666667</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B64" s="2">
-        <v>45986.622917002314</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="D64" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -3124,16 +3161,16 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B65" s="3">
+        <v>45986.501388888886</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B65" s="2">
-        <v>45986.501389004632</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="D65" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -3147,16 +3184,16 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B66" s="3">
+        <v>45986.484027777777</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B66" s="2">
-        <v>45986.484027997685</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="D66" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -3170,16 +3207,16 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B67" s="2">
-        <v>45986.483332997683</v>
+        <v>214</v>
+      </c>
+      <c r="B67" s="3">
+        <v>45986.48333333333</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E67">
         <v>100</v>
@@ -3193,16 +3230,16 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B68" s="2">
-        <v>45986.461805995372</v>
+        <v>215</v>
+      </c>
+      <c r="B68" s="3">
+        <v>45986.461805555555</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -3216,16 +3253,16 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B69" s="3">
+        <v>45986.443749999999</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B69" s="2">
-        <v>45986.443749999999</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="D69" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -3239,16 +3276,16 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B70" s="2">
-        <v>45986.377777997688</v>
+        <v>218</v>
+      </c>
+      <c r="B70" s="3">
+        <v>45986.37777777778</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -3262,16 +3299,16 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B71" s="2">
-        <v>45986.376389004632</v>
+        <v>219</v>
+      </c>
+      <c r="B71" s="3">
+        <v>45986.376388888886</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -3285,16 +3322,16 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B72" s="2">
-        <v>45986.376389004632</v>
+        <v>219</v>
+      </c>
+      <c r="B72" s="3">
+        <v>45986.376388888886</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -3308,16 +3345,16 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B73" s="2">
-        <v>45986.373610995368</v>
+        <v>220</v>
+      </c>
+      <c r="B73" s="3">
+        <v>45986.373611111114</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E73">
         <v>200</v>
@@ -3331,16 +3368,16 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B74" s="2">
+        <v>221</v>
+      </c>
+      <c r="B74" s="3">
         <v>45985.887499999997</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3354,16 +3391,16 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B75" s="2">
-        <v>45985.882639004631</v>
+        <v>222</v>
+      </c>
+      <c r="B75" s="3">
+        <v>45985.882638888892</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -3377,16 +3414,16 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B76" s="3">
+        <v>45985.861111111109</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B76" s="2">
-        <v>45985.861110995371</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="D76" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3400,16 +3437,16 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B77" s="3">
+        <v>45985.854861111111</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B77" s="2">
-        <v>45985.854860995372</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="D77" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3423,16 +3460,16 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B78" s="3">
+        <v>45985.777083333334</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B78" s="2">
-        <v>45985.777082997687</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="D78" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3446,16 +3483,16 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B79" s="2">
-        <v>45985.776389004626</v>
+        <v>229</v>
+      </c>
+      <c r="B79" s="3">
+        <v>45985.776388888888</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3469,16 +3506,16 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B80" s="2">
-        <v>45985.775694004631</v>
+        <v>230</v>
+      </c>
+      <c r="B80" s="3">
+        <v>45985.775694444441</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E80">
         <v>200</v>
@@ -3492,16 +3529,16 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B81" s="3">
+        <v>45985.768055555556</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B81" s="2">
-        <v>45985.768055995373</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="D81" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -3515,16 +3552,16 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B82" s="3">
+        <v>45985.676388888889</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B82" s="2">
-        <v>45985.676389004628</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="D82" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3538,16 +3575,16 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B83" s="2">
-        <v>45985.676389004628</v>
+        <v>235</v>
+      </c>
+      <c r="B83" s="3">
+        <v>45985.676388888889</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E83">
         <v>100</v>
@@ -3561,16 +3598,16 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B84" s="3">
+        <v>45985.354861111111</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B84" s="2">
-        <v>45985.354860995372</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="D84" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3584,16 +3621,16 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B85" s="3">
+        <v>45985.350694444445</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B85" s="2">
-        <v>45985.350694004628</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="D85" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3607,16 +3644,16 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B86" s="3">
+        <v>45985.302083333336</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B86" s="2">
-        <v>45985.302082997689</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="D86" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3630,16 +3667,16 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B87" s="3">
+        <v>45985.290277777778</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B87" s="2">
-        <v>45985.290277997687</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="D87" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3653,16 +3690,16 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B88" s="2">
-        <v>45985.289582997684</v>
+        <v>244</v>
+      </c>
+      <c r="B88" s="3">
+        <v>45985.289583333331</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E88">
         <v>200</v>
@@ -3676,16 +3713,16 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B89" s="3">
+        <v>45984.845833333333</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B89" s="2">
-        <v>45984.845832997686</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="D89" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3699,16 +3736,16 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B90" s="2">
-        <v>45984.832639004628</v>
+        <v>247</v>
+      </c>
+      <c r="B90" s="3">
+        <v>45984.832638888889</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3722,16 +3759,16 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B91" s="2">
-        <v>45984.796527997685</v>
+        <v>248</v>
+      </c>
+      <c r="B91" s="3">
+        <v>45984.796527777777</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3745,16 +3782,16 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B92" s="2">
-        <v>45984.795832997683</v>
+        <v>249</v>
+      </c>
+      <c r="B92" s="3">
+        <v>45984.79583333333</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E92">
         <v>100</v>
@@ -3768,16 +3805,16 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B93" s="2">
-        <v>45984.773610995369</v>
+        <v>250</v>
+      </c>
+      <c r="B93" s="3">
+        <v>45984.773611111108</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3791,16 +3828,16 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B94" s="2">
-        <v>45984.743055995372</v>
+        <v>251</v>
+      </c>
+      <c r="B94" s="3">
+        <v>45984.743055555555</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3814,16 +3851,16 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B95" s="2">
-        <v>45984.742360995369</v>
+        <v>252</v>
+      </c>
+      <c r="B95" s="3">
+        <v>45984.742361111108</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E95">
         <v>100</v>
@@ -3837,16 +3874,16 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B96" s="2">
-        <v>45984.741667002316</v>
+        <v>253</v>
+      </c>
+      <c r="B96" s="3">
+        <v>45984.741666666669</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3860,16 +3897,16 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B97" s="3">
+        <v>45984.734027777777</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B97" s="2">
-        <v>45984.734027997685</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="D97" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3883,16 +3920,16 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B98" s="2">
+        <v>256</v>
+      </c>
+      <c r="B98" s="3">
         <v>45984.724999999999</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E98">
         <v>150</v>
@@ -3906,16 +3943,16 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B99" s="2">
-        <v>45984.720139004632</v>
+        <v>257</v>
+      </c>
+      <c r="B99" s="3">
+        <v>45984.720138888886</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3929,16 +3966,16 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B100" s="3">
+        <v>45984.640277777777</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B100" s="2">
-        <v>45984.640277997685</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="D100" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3952,16 +3989,16 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B101" s="2">
-        <v>45984.466667002314</v>
+        <v>260</v>
+      </c>
+      <c r="B101" s="3">
+        <v>45984.466666666667</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3975,16 +4012,16 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B102" s="3">
+        <v>45984.447222222225</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B102" s="2">
-        <v>45984.447222002316</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="D102" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3998,16 +4035,16 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B103" s="2">
-        <v>45984.419444004627</v>
+        <v>263</v>
+      </c>
+      <c r="B103" s="3">
+        <v>45984.419444444444</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4021,16 +4058,16 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B104" s="3">
+        <v>45984.419444444444</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B104" s="2">
-        <v>45984.419444004627</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="D104" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4044,16 +4081,16 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B105" s="2">
-        <v>45984.418055995367</v>
+        <v>265</v>
+      </c>
+      <c r="B105" s="3">
+        <v>45984.418055555558</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -4067,16 +4104,16 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B106" s="2">
-        <v>45984.384027997687</v>
+        <v>266</v>
+      </c>
+      <c r="B106" s="3">
+        <v>45984.384027777778</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -4090,16 +4127,16 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B107" s="3">
+        <v>45983.956250000003</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B107" s="2">
-        <v>45983.956250000003</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="D107" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -4113,16 +4150,16 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B108" s="2">
-        <v>45983.955555995373</v>
+        <v>269</v>
+      </c>
+      <c r="B108" s="3">
+        <v>45983.955555555556</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E108">
         <v>200</v>
@@ -4136,16 +4173,16 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B109" s="2">
-        <v>45983.908332997686</v>
+        <v>270</v>
+      </c>
+      <c r="B109" s="3">
+        <v>45983.908333333333</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -4159,16 +4196,16 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="B110" s="2">
-        <v>45983.90694400463</v>
+        <v>271</v>
+      </c>
+      <c r="B110" s="3">
+        <v>45983.906944444447</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4182,16 +4219,16 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="B111" s="2">
-        <v>45983.90694400463</v>
+        <v>272</v>
+      </c>
+      <c r="B111" s="3">
+        <v>45983.906944444447</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E111">
         <v>100</v>
@@ -4205,16 +4242,16 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B112" s="3">
+        <v>45983.899305555555</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B112" s="2">
-        <v>45983.899305995372</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="D112" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -4228,16 +4265,16 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B113" s="3">
+        <v>45983.815972222219</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B113" s="2">
-        <v>45983.815972002318</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="D113" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -4251,16 +4288,16 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B114" s="2">
-        <v>45983.815277997688</v>
+        <v>277</v>
+      </c>
+      <c r="B114" s="3">
+        <v>45983.81527777778</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4274,16 +4311,16 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B115" s="2">
-        <v>45983.802777997684</v>
+        <v>278</v>
+      </c>
+      <c r="B115" s="3">
+        <v>45983.802777777775</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4297,16 +4334,16 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B116" s="3">
+        <v>45983.636805555558</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B116" s="2">
-        <v>45983.636805995367</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="D116" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4320,16 +4357,16 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B117" s="2">
-        <v>45983.619444004631</v>
+        <v>281</v>
+      </c>
+      <c r="B117" s="3">
+        <v>45983.619444444441</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E117">
         <v>2000</v>
@@ -4343,16 +4380,16 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B118" s="2">
-        <v>45983.602777997687</v>
+        <v>282</v>
+      </c>
+      <c r="B118" s="3">
+        <v>45983.602777777778</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4366,16 +4403,16 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B119" s="2">
-        <v>45983.422222002315</v>
+        <v>283</v>
+      </c>
+      <c r="B119" s="3">
+        <v>45983.422222222223</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4389,16 +4426,16 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B120" s="3">
+        <v>45983.396527777775</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B120" s="2">
-        <v>45983.396527997684</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="D120" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4412,16 +4449,16 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B121" s="3">
+        <v>45983.35833333333</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B121" s="2">
-        <v>45983.358332997683</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="D121" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4435,16 +4472,16 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B122" s="3">
+        <v>45983.341666666667</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B122" s="2">
-        <v>45983.341667002314</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="D122" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4458,16 +4495,16 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B123" s="2">
-        <v>45983.334722002313</v>
+        <v>290</v>
+      </c>
+      <c r="B123" s="3">
+        <v>45983.334722222222</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4481,16 +4518,16 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B124" s="2">
-        <v>45982.871527997682</v>
+        <v>291</v>
+      </c>
+      <c r="B124" s="3">
+        <v>45982.871527777781</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4504,16 +4541,16 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B125" s="2">
-        <v>45982.865972002313</v>
+        <v>292</v>
+      </c>
+      <c r="B125" s="3">
+        <v>45982.865972222222</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4527,16 +4564,16 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B126" s="3">
+        <v>45982.862500000003</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B126" s="2">
-        <v>45982.862500000003</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="D126" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4550,16 +4587,16 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B127" s="3">
+        <v>45982.855555555558</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B127" s="2">
-        <v>45982.855555995367</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="D127" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4573,16 +4610,16 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B128" s="2">
-        <v>45982.802082997689</v>
+        <v>297</v>
+      </c>
+      <c r="B128" s="3">
+        <v>45982.802083333336</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4596,16 +4633,16 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B129" s="3">
+        <v>45982.802083333336</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B129" s="2">
-        <v>45982.802082997689</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="D129" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4619,16 +4656,16 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B130" s="3">
+        <v>45982.77847222222</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B130" s="2">
-        <v>45982.778472002312</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="D130" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4642,16 +4679,16 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B131" s="3">
+        <v>45982.768750000003</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B131" s="2">
-        <v>45982.768750000003</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="D131" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4665,16 +4702,16 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B132" s="2">
+        <v>303</v>
+      </c>
+      <c r="B132" s="3">
         <v>45982.762499999997</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4688,16 +4725,16 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B133" s="2">
-        <v>45982.761110995372</v>
+        <v>304</v>
+      </c>
+      <c r="B133" s="3">
+        <v>45982.761111111111</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4711,16 +4748,16 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B134" s="3">
+        <v>45982.662499999999</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B134" s="2">
-        <v>45982.662499999999</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="D134" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4734,16 +4771,16 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B135" s="3">
+        <v>45982.646527777775</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B135" s="2">
-        <v>45982.646527997684</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="D135" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E135">
         <v>15500</v>
@@ -4757,16 +4794,16 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B136" s="2">
-        <v>45982.584027997684</v>
+        <v>309</v>
+      </c>
+      <c r="B136" s="3">
+        <v>45982.584027777775</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4780,16 +4817,16 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B137" s="3">
+        <v>45982.359722222223</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B137" s="2">
-        <v>45982.359722002315</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="D137" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4803,16 +4840,16 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B138" s="2">
-        <v>45982.305555995372</v>
+        <v>312</v>
+      </c>
+      <c r="B138" s="3">
+        <v>45982.305555555555</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4826,16 +4863,16 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B139" s="2">
-        <v>45982.297222002315</v>
+        <v>313</v>
+      </c>
+      <c r="B139" s="3">
+        <v>45982.297222222223</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E139">
         <v>1000</v>
@@ -4849,16 +4886,16 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B140" s="3">
+        <v>45982.29583333333</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B140" s="2">
-        <v>45982.295832997683</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="D140" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4872,16 +4909,16 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B141" s="3">
+        <v>45982.293055555558</v>
+      </c>
+      <c r="C141" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B141" s="2">
-        <v>45982.293055995367</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="D141" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4895,16 +4932,16 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B142" s="3">
+        <v>45981.919444444444</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B142" s="2">
-        <v>45981.919444004627</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="D142" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4918,16 +4955,16 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B143" s="2">
-        <v>45981.917360995372</v>
+        <v>320</v>
+      </c>
+      <c r="B143" s="3">
+        <v>45981.917361111111</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4941,16 +4978,16 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B144" s="2">
-        <v>45981.896527997684</v>
+        <v>321</v>
+      </c>
+      <c r="B144" s="3">
+        <v>45981.896527777775</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E144">
         <v>200</v>
@@ -4964,16 +5001,16 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B145" s="2">
-        <v>45981.879167002313</v>
+        <v>322</v>
+      </c>
+      <c r="B145" s="3">
+        <v>45981.879166666666</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -4987,16 +5024,16 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B146" s="3">
+        <v>45981.842361111114</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B146" s="2">
-        <v>45981.842360995368</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="D146" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5010,16 +5047,16 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" s="3">
+        <v>45981.837500000001</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B147" s="2">
-        <v>45981.837500000001</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="D147" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5033,16 +5070,16 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B148" s="3">
+        <v>45981.836111111108</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B148" s="2">
-        <v>45981.836110995369</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="D148" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5056,16 +5093,16 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B149" s="2">
-        <v>45981.834722002313</v>
+        <v>329</v>
+      </c>
+      <c r="B149" s="3">
+        <v>45981.834722222222</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5079,16 +5116,16 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B150" s="2">
-        <v>45981.834722002313</v>
+        <v>329</v>
+      </c>
+      <c r="B150" s="3">
+        <v>45981.834722222222</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5102,16 +5139,16 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B151" s="2">
-        <v>45981.823610995372</v>
+        <v>330</v>
+      </c>
+      <c r="B151" s="3">
+        <v>45981.823611111111</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5125,16 +5162,16 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B152" s="3">
+        <v>45981.777083333334</v>
+      </c>
+      <c r="C152" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B152" s="2">
-        <v>45981.777082997687</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="D152" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5148,16 +5185,16 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B153" s="2">
-        <v>45981.776389004626</v>
+        <v>333</v>
+      </c>
+      <c r="B153" s="3">
+        <v>45981.776388888888</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5171,16 +5208,16 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B154" s="3">
+        <v>45981.749305555553</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B154" s="2">
-        <v>45981.74930599537</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="D154" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -5194,16 +5231,16 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B155" s="2">
-        <v>45981.514582997683</v>
+        <v>336</v>
+      </c>
+      <c r="B155" s="3">
+        <v>45981.51458333333</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5217,16 +5254,16 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B156" s="3">
+        <v>45981.395138888889</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B156" s="2">
-        <v>45981.395139004628</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="D156" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5240,16 +5277,16 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B157" s="2">
-        <v>45981.368055995372</v>
+        <v>339</v>
+      </c>
+      <c r="B157" s="3">
+        <v>45981.368055555555</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5263,16 +5300,16 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B158" s="2">
-        <v>45981.342360995368</v>
+        <v>340</v>
+      </c>
+      <c r="B158" s="3">
+        <v>45981.342361111114</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5286,16 +5323,16 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B159" s="3">
+        <v>45981.332638888889</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B159" s="2">
-        <v>45981.332639004628</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="D159" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5309,16 +5346,16 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="B160" s="2">
-        <v>45980.911805995369</v>
+        <v>343</v>
+      </c>
+      <c r="B160" s="3">
+        <v>45980.911805555559</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5332,16 +5369,16 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="B161" s="2">
-        <v>45980.890277997685</v>
+        <v>344</v>
+      </c>
+      <c r="B161" s="3">
+        <v>45980.890277777777</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5355,16 +5392,16 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B162" s="2">
-        <v>45980.885417002311</v>
+        <v>162</v>
+      </c>
+      <c r="B162" s="3">
+        <v>45980.885416666664</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5378,16 +5415,16 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B163" s="3">
+        <v>45980.878472222219</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B163" s="2">
-        <v>45980.878472002318</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="D163" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5401,16 +5438,16 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B164" s="3">
+        <v>45980.870833333334</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B164" s="2">
-        <v>45980.870832997687</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="D164" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5424,16 +5461,16 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B165" s="3">
+        <v>45980.852777777778</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B165" s="2">
-        <v>45980.852777997687</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="D165" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5447,16 +5484,16 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B166" s="3">
+        <v>45980.836805555555</v>
+      </c>
+      <c r="C166" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B166" s="2">
-        <v>45980.836805995372</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="D166" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5470,16 +5507,16 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B167" s="3">
+        <v>45980.783333333333</v>
+      </c>
+      <c r="C167" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B167" s="2">
-        <v>45980.783332997686</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="D167" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5493,16 +5530,16 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B168" s="2">
-        <v>45980.783332997686</v>
+        <v>173</v>
+      </c>
+      <c r="B168" s="3">
+        <v>45980.783333333333</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5516,16 +5553,16 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B169" s="2">
-        <v>45980.761805995367</v>
+        <v>174</v>
+      </c>
+      <c r="B169" s="3">
+        <v>45980.761805555558</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5539,16 +5576,16 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B170" s="3">
+        <v>45980.344444444447</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B170" s="2">
-        <v>45980.34444400463</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="D170" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5562,16 +5599,16 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B171" s="3">
+        <v>45980.290972222225</v>
+      </c>
+      <c r="C171" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B171" s="2">
-        <v>45980.290972002316</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="D171" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5585,16 +5622,16 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B172" s="3">
+        <v>45980.282638888886</v>
+      </c>
+      <c r="C172" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B172" s="2">
-        <v>45980.282639004632</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="D172" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5608,16 +5645,16 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B173" s="2">
-        <v>45979.891667002317</v>
+        <v>181</v>
+      </c>
+      <c r="B173" s="3">
+        <v>45979.89166666667</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5631,16 +5668,16 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B174" s="2">
-        <v>45979.87569400463</v>
+        <v>182</v>
+      </c>
+      <c r="B174" s="3">
+        <v>45979.875694444447</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5654,16 +5691,16 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B175" s="2">
+        <v>183</v>
+      </c>
+      <c r="B175" s="3">
         <v>45979.875</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5677,16 +5714,16 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B176" s="3">
+        <v>45979.873611111114</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B176" s="2">
-        <v>45979.873610995368</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="D176" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -5700,16 +5737,16 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B177" s="3">
+        <v>45979.847916666666</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B177" s="2">
-        <v>45979.847917002313</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="D177" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -5723,16 +5760,16 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B178" s="3">
+        <v>45979.838194444441</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B178" s="2">
-        <v>45979.838194004631</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="D178" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -5746,16 +5783,16 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B179" s="3">
+        <v>45979.779166666667</v>
+      </c>
+      <c r="C179" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B179" s="2">
-        <v>45979.779167002314</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="D179" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -5769,16 +5806,16 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B180" s="2">
-        <v>45979.778472002312</v>
+        <v>192</v>
+      </c>
+      <c r="B180" s="3">
+        <v>45979.77847222222</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -5792,16 +5829,16 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B181" s="2">
-        <v>45979.742360995369</v>
+        <v>193</v>
+      </c>
+      <c r="B181" s="3">
+        <v>45979.742361111108</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -5815,16 +5852,16 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B182" s="3">
+        <v>45979.742361111108</v>
+      </c>
+      <c r="C182" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B182" s="2">
-        <v>45979.742360995369</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="D182" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -5838,16 +5875,16 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B183" s="3">
+        <v>45979.727777777778</v>
+      </c>
+      <c r="C183" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B183" s="2">
-        <v>45979.727777997687</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="D183" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -5861,16 +5898,16 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B184" s="2">
-        <v>45979.709027997684</v>
+        <v>197</v>
+      </c>
+      <c r="B184" s="3">
+        <v>45979.709027777775</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -5884,16 +5921,16 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B185" s="3">
+        <v>45979.709027777775</v>
+      </c>
+      <c r="C185" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B185" s="2">
-        <v>45979.709027997684</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="D185" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -5907,16 +5944,16 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B186" s="2">
-        <v>45979.707639004628</v>
+        <v>199</v>
+      </c>
+      <c r="B186" s="3">
+        <v>45979.707638888889</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E186">
         <v>7000</v>
@@ -5930,16 +5967,16 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B187" s="2">
+        <v>200</v>
+      </c>
+      <c r="B187" s="3">
         <v>45979.7</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -5953,16 +5990,16 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B188" s="2">
+        <v>201</v>
+      </c>
+      <c r="B188" s="3">
         <v>45979.506249999999</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E188">
         <v>200</v>
@@ -5976,16 +6013,16 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B189" s="3">
+        <v>45979.497916666667</v>
+      </c>
+      <c r="C189" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B189" s="2">
-        <v>45979.497917002314</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="D189" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -5999,16 +6036,16 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B190" s="2">
-        <v>45979.493055995372</v>
+        <v>204</v>
+      </c>
+      <c r="B190" s="3">
+        <v>45979.493055555555</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6022,16 +6059,16 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B191" s="3">
+        <v>45979.48541666667</v>
+      </c>
+      <c r="C191" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B191" s="2">
-        <v>45979.485417002317</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="D191" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6045,16 +6082,16 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B192" s="3">
+        <v>45979.479166666664</v>
+      </c>
+      <c r="C192" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B192" s="2">
-        <v>45979.479167002311</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="D192" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6068,16 +6105,16 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B193" s="3">
+        <v>45979.447222222225</v>
+      </c>
+      <c r="C193" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B193" s="2">
-        <v>45979.447222002316</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="D193" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6091,16 +6128,16 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B194" s="2">
-        <v>45979.43819400463</v>
+        <v>211</v>
+      </c>
+      <c r="B194" s="3">
+        <v>45979.438194444447</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E194">
         <v>200</v>
@@ -6114,16 +6151,16 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B195" s="2">
-        <v>45979.413194004628</v>
+        <v>345</v>
+      </c>
+      <c r="B195" s="3">
+        <v>45979.413194444445</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6137,16 +6174,16 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="B196" s="2">
-        <v>45978.879167002313</v>
+        <v>346</v>
+      </c>
+      <c r="B196" s="3">
+        <v>45978.879166666666</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -6160,16 +6197,16 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B197" s="2">
-        <v>45978.865972002313</v>
+        <v>347</v>
+      </c>
+      <c r="B197" s="3">
+        <v>45978.865972222222</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -6183,16 +6220,16 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B198" s="3">
+        <v>45978.850694444445</v>
+      </c>
+      <c r="C198" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B198" s="2">
-        <v>45978.850694004628</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="D198" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6206,16 +6243,16 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B199" s="2">
+        <v>350</v>
+      </c>
+      <c r="B199" s="3">
         <v>45978.85</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E199">
         <v>100</v>
@@ -6229,16 +6266,16 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B200" s="3">
+        <v>45978.802083333336</v>
+      </c>
+      <c r="C200" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B200" s="2">
-        <v>45978.802082997689</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="D200" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6252,16 +6289,16 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B201" s="2">
-        <v>45978.801389004628</v>
+        <v>353</v>
+      </c>
+      <c r="B201" s="3">
+        <v>45978.801388888889</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6275,16 +6312,16 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B202" s="2">
-        <v>45978.764582997683</v>
+        <v>354</v>
+      </c>
+      <c r="B202" s="3">
+        <v>45978.76458333333</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6298,16 +6335,16 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B203" s="2">
-        <v>45978.756944004628</v>
+        <v>355</v>
+      </c>
+      <c r="B203" s="3">
+        <v>45978.756944444445</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E203">
         <v>200</v>
@@ -6321,16 +6358,16 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B204" s="3">
+        <v>45978.379861111112</v>
+      </c>
+      <c r="C204" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B204" s="2">
-        <v>45978.379860995374</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="D204" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6344,16 +6381,16 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B205" s="2">
-        <v>45978.379167002313</v>
+        <v>358</v>
+      </c>
+      <c r="B205" s="3">
+        <v>45978.379166666666</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6367,16 +6404,16 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B206" s="3">
+        <v>45978.302777777775</v>
+      </c>
+      <c r="C206" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B206" s="2">
-        <v>45978.302777997684</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="D206" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6390,16 +6427,16 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B207" s="2">
-        <v>45978.293055995367</v>
+        <v>361</v>
+      </c>
+      <c r="B207" s="3">
+        <v>45978.293055555558</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -6413,16 +6450,16 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B208" s="3">
+        <v>45978.280555555553</v>
+      </c>
+      <c r="C208" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B208" s="2">
-        <v>45978.28055599537</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="D208" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -6436,16 +6473,16 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B209" s="2">
+        <v>364</v>
+      </c>
+      <c r="B209" s="3">
         <v>45978.275000000001</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E209">
         <v>200</v>
@@ -6459,16 +6496,16 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="B210" s="2">
-        <v>45977.901389004626</v>
+        <v>365</v>
+      </c>
+      <c r="B210" s="3">
+        <v>45977.901388888888</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -6482,16 +6519,16 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="B211" s="2">
+        <v>366</v>
+      </c>
+      <c r="B211" s="3">
         <v>45977.9</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -6505,16 +6542,16 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B212" s="3">
+        <v>45977.898611111108</v>
+      </c>
+      <c r="C212" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B212" s="2">
-        <v>45977.898610995369</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="D212" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -6528,16 +6565,16 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="B213" s="2">
-        <v>45977.71805599537</v>
+        <v>369</v>
+      </c>
+      <c r="B213" s="3">
+        <v>45977.718055555553</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -6551,16 +6588,16 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B214" s="2">
-        <v>45977.717360995368</v>
+        <v>370</v>
+      </c>
+      <c r="B214" s="3">
+        <v>45977.717361111114</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E214">
         <v>100</v>
@@ -6574,16 +6611,16 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="B215" s="2">
-        <v>45977.690972002318</v>
+        <v>371</v>
+      </c>
+      <c r="B215" s="3">
+        <v>45977.690972222219</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -6597,16 +6634,16 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B216" s="2">
-        <v>45977.641667002317</v>
+        <v>372</v>
+      </c>
+      <c r="B216" s="3">
+        <v>45977.64166666667</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -6620,16 +6657,16 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B217" s="3">
+        <v>45977.64166666667</v>
+      </c>
+      <c r="C217" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B217" s="2">
-        <v>45977.641667002317</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="D217" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -6643,16 +6680,16 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B218" s="2">
+        <v>374</v>
+      </c>
+      <c r="B218" s="3">
         <v>45977.518750000003</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -6666,16 +6703,16 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B219" s="2">
-        <v>45977.496527997682</v>
+        <v>375</v>
+      </c>
+      <c r="B219" s="3">
+        <v>45977.496527777781</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E219">
         <v>200</v>
@@ -6689,16 +6726,16 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="B220" s="2">
-        <v>45977.495832997687</v>
+        <v>376</v>
+      </c>
+      <c r="B220" s="3">
+        <v>45977.495833333334</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -6712,16 +6749,16 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="B221" s="2">
-        <v>45976.914582997684</v>
+        <v>377</v>
+      </c>
+      <c r="B221" s="3">
+        <v>45976.914583333331</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -6735,16 +6772,16 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B222" s="3">
+        <v>45976.911111111112</v>
+      </c>
+      <c r="C222" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B222" s="2">
-        <v>45976.911110995374</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="D222" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -6758,16 +6795,16 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B223" s="3">
+        <v>45976.882638888892</v>
+      </c>
+      <c r="C223" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B223" s="2">
-        <v>45976.882639004631</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D223" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -6781,16 +6818,16 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="B224" s="2">
-        <v>45976.878472002318</v>
+        <v>382</v>
+      </c>
+      <c r="B224" s="3">
+        <v>45976.878472222219</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E224">
         <v>100</v>
@@ -6804,16 +6841,16 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="B225" s="2">
-        <v>45976.854167002311</v>
+        <v>383</v>
+      </c>
+      <c r="B225" s="3">
+        <v>45976.854166666664</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -6827,16 +6864,16 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="B226" s="2">
-        <v>45976.847222002318</v>
+        <v>384</v>
+      </c>
+      <c r="B226" s="3">
+        <v>45976.847222222219</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -6850,16 +6887,16 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B227" s="3">
+        <v>45976.842361111114</v>
+      </c>
+      <c r="C227" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B227" s="2">
-        <v>45976.842360995368</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="D227" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -6873,16 +6910,16 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B228" s="3">
+        <v>45976.761805555558</v>
+      </c>
+      <c r="C228" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B228" s="2">
-        <v>45976.761805995367</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="D228" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -6896,16 +6933,16 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B229" s="2">
-        <v>45976.761110995372</v>
+        <v>64</v>
+      </c>
+      <c r="B229" s="3">
+        <v>45976.761111111111</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -6919,16 +6956,16 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B230" s="2">
-        <v>45976.752082997686</v>
+        <v>65</v>
+      </c>
+      <c r="B230" s="3">
+        <v>45976.752083333333</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E230">
         <v>200</v>
@@ -6942,16 +6979,16 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B231" s="2">
+        <v>66</v>
+      </c>
+      <c r="B231" s="3">
         <v>45976.368750000001</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -6965,16 +7002,16 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B232" s="3">
+        <v>45976.353472222225</v>
+      </c>
+      <c r="C232" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B232" s="2">
-        <v>45976.353472002316</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="D232" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -6988,16 +7025,16 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B233" s="3">
+        <v>45976.348611111112</v>
+      </c>
+      <c r="C233" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B233" s="2">
-        <v>45976.348610995374</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="D233" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7011,16 +7048,16 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B234" s="3">
+        <v>45976.311111111114</v>
+      </c>
+      <c r="C234" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B234" s="2">
-        <v>45976.311110995368</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="D234" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7034,16 +7071,16 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B235" s="3">
+        <v>45976.29583333333</v>
+      </c>
+      <c r="C235" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B235" s="2">
-        <v>45976.295832997683</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="D235" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7057,16 +7094,16 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B236" s="2">
-        <v>45975.879167002313</v>
+        <v>75</v>
+      </c>
+      <c r="B236" s="3">
+        <v>45975.879166666666</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7080,16 +7117,16 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B237" s="3">
+        <v>45975.876388888886</v>
+      </c>
+      <c r="C237" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B237" s="2">
-        <v>45975.876389004632</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="D237" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7103,16 +7140,16 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B238" s="3">
+        <v>45975.870833333334</v>
+      </c>
+      <c r="C238" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B238" s="2">
-        <v>45975.870832997687</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="D238" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7126,16 +7163,16 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B239" s="3">
+        <v>45975.864583333336</v>
+      </c>
+      <c r="C239" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B239" s="2">
-        <v>45975.864582997689</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="D239" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -7149,16 +7186,16 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B240" s="3">
+        <v>45975.859722222223</v>
+      </c>
+      <c r="C240" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B240" s="2">
-        <v>45975.859722002315</v>
-      </c>
-      <c r="C240" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="D240" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -7172,16 +7209,16 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B241" s="2">
-        <v>45975.859722002315</v>
+        <v>82</v>
+      </c>
+      <c r="B241" s="3">
+        <v>45975.859722222223</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -7195,16 +7232,16 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B242" s="2">
-        <v>45975.858332997683</v>
+        <v>85</v>
+      </c>
+      <c r="B242" s="3">
+        <v>45975.85833333333</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E242">
         <v>3500</v>
@@ -7218,16 +7255,16 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B243" s="2">
-        <v>45975.796527997685</v>
+        <v>86</v>
+      </c>
+      <c r="B243" s="3">
+        <v>45975.796527777777</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -7241,16 +7278,16 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B244" s="3">
+        <v>45975.777083333334</v>
+      </c>
+      <c r="C244" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B244" s="2">
-        <v>45975.777082997687</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="D244" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -7264,16 +7301,16 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B245" s="2">
-        <v>45975.777082997687</v>
+        <v>89</v>
+      </c>
+      <c r="B245" s="3">
+        <v>45975.777083333334</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -7287,16 +7324,16 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B246" s="3">
+        <v>45975.756944444445</v>
+      </c>
+      <c r="C246" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B246" s="2">
-        <v>45975.756944004628</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="D246" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -7310,16 +7347,16 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B247" s="3">
+        <v>45991.90625</v>
+      </c>
+      <c r="C247" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B247" s="2">
-        <v>45991.90625</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="D247" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -7333,16 +7370,16 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B248" s="2">
-        <v>45991.901389004626</v>
+        <v>94</v>
+      </c>
+      <c r="B248" s="3">
+        <v>45991.901388888888</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -7356,16 +7393,16 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B249" s="2">
-        <v>45991.899305995372</v>
+        <v>95</v>
+      </c>
+      <c r="B249" s="3">
+        <v>45991.899305555555</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -7379,16 +7416,16 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B250" s="3">
+        <v>45991.71875</v>
+      </c>
+      <c r="C250" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B250" s="2">
-        <v>45991.71875</v>
-      </c>
-      <c r="C250" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="D250" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -7402,16 +7439,16 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B251" s="3">
+        <v>45991.708333333336</v>
+      </c>
+      <c r="C251" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B251" s="2">
-        <v>45991.708332997689</v>
-      </c>
-      <c r="C251" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="D251" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E251">
         <v>500</v>
@@ -7425,16 +7462,16 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B252" s="2">
-        <v>45991.653472002312</v>
+        <v>100</v>
+      </c>
+      <c r="B252" s="3">
+        <v>45991.65347222222</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -7448,16 +7485,16 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B253" s="2">
-        <v>45991.584722002313</v>
+        <v>101</v>
+      </c>
+      <c r="B253" s="3">
+        <v>45991.584722222222</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -7471,16 +7508,16 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B254" s="3">
+        <v>45991.381249999999</v>
+      </c>
+      <c r="C254" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B254" s="2">
-        <v>45991.381249999999</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="D254" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -7494,16 +7531,16 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B255" s="3">
+        <v>45991.376388888886</v>
+      </c>
+      <c r="C255" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B255" s="2">
-        <v>45991.376389004632</v>
-      </c>
-      <c r="C255" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="D255" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -7517,16 +7554,16 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B256" s="2">
-        <v>45991.376389004632</v>
+        <v>104</v>
+      </c>
+      <c r="B256" s="3">
+        <v>45991.376388888886</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -7540,16 +7577,16 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B257" s="2">
-        <v>45991.37569400463</v>
+        <v>107</v>
+      </c>
+      <c r="B257" s="3">
+        <v>45991.375694444447</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E257">
         <v>100</v>
@@ -7563,16 +7600,16 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B258" s="2">
-        <v>45991.372222002312</v>
+        <v>108</v>
+      </c>
+      <c r="B258" s="3">
+        <v>45991.37222222222</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E258">
         <v>200</v>
@@ -7586,16 +7623,16 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B259" s="2">
-        <v>45990.925694004633</v>
+        <v>109</v>
+      </c>
+      <c r="B259" s="3">
+        <v>45990.925694444442</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -7609,16 +7646,16 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B260" s="3">
+        <v>45990.904861111114</v>
+      </c>
+      <c r="C260" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B260" s="2">
-        <v>45990.904860995368</v>
-      </c>
-      <c r="C260" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="D260" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -7631,9 +7668,11 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
